--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5664638-F673-4179-8E70-4D19BECF7E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE1E5BC-DA59-4BF1-B87D-4BA222FB5056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -67,14 +67,6 @@
     <t>E- tier</t>
   </si>
   <si>
-    <t>Divine</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>∞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>small stack=</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -111,26 +103,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>div/chaos &gt;=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>delta=</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>(div/chaos)^0.25=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(div/chaos)^(1/3)=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(div/chaos)^0.2=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>D tier chaos</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -159,10 +135,6 @@
   </si>
   <si>
     <t>1/r³</t>
-  </si>
-  <si>
-    <t>&lt;=r&lt;=</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>r=</t>
@@ -199,6 +171,67 @@
       <t>4</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="24"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>∞</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="24"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="24"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="24"/>
+        <color theme="0" tint="-0.14999847407452621"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>≤</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S tier/chaos &gt;=</t>
+  </si>
+  <si>
+    <t>(S tier/chaos)^0.25=</t>
+  </si>
+  <si>
+    <t>(S tier/chaos)^(1/3)=</t>
+  </si>
+  <si>
+    <t>(S tier/chaos)^0.2=</t>
   </si>
 </sst>
 </file>
@@ -209,7 +242,7 @@
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +287,13 @@
       <color rgb="FF0DB374"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -725,23 +765,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.125" style="1"/>
+    <col min="3" max="4" width="16.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.75" style="1" customWidth="1"/>
+    <col min="8" max="8" width="37.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="3"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -750,286 +789,275 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="3"/>
       <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="3"/>
       <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="6">
         <f>D3</f>
-        <v>26.375378043300007</v>
+        <v>52.750756086600013</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="9">
+        <f>C2/1</f>
+        <v>52.750756086600013</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="9">
-        <f>C2/1</f>
-        <v>26.375378043300007</v>
-      </c>
-      <c r="I2" s="5"/>
-      <c r="J2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="10">
-        <v>3</v>
-      </c>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J2" s="10">
+        <v>4</v>
+      </c>
+      <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3"/>
       <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="11">
         <f t="shared" ref="C3:C9" si="0">D4</f>
-        <v>8.8211966700000026</v>
+        <v>17.642393340000005</v>
       </c>
       <c r="D3" s="5">
-        <f>D7*I10^4</f>
-        <v>26.375378043300007</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="8" t="s">
+        <f>D7*H10^4</f>
+        <v>52.750756086600013</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="9">
-        <f>H2^0.25</f>
-        <v>2.2662075040983041</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="K3" s="10">
-        <v>9</v>
-      </c>
-      <c r="L3" s="3"/>
-    </row>
-    <row r="4" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="F3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="9">
+        <f>G2^0.25</f>
+        <v>2.6949900879462607</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="10">
+        <v>16</v>
+      </c>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A4" s="3"/>
       <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="11">
         <f>D5</f>
-        <v>2.9502330000000003</v>
+        <v>5.9004660000000007</v>
       </c>
       <c r="D4" s="5">
-        <f>D7*I10^3</f>
-        <v>8.8211966700000026</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="8" t="s">
+        <f>D7*H10^3</f>
+        <v>17.642393340000005</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="9">
-        <f>H2^(1/3)</f>
-        <v>2.9766851284351317</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="9">
-        <f>SQRT(K3)</f>
-        <v>3</v>
-      </c>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="9">
+        <f>G2^(1/3)</f>
+        <v>3.7503882522244463</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="9">
+        <f>SQRT(J3)</f>
+        <v>4</v>
+      </c>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3"/>
       <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="11">
         <f>D6</f>
-        <v>0.98670000000000013</v>
+        <v>1.9734000000000003</v>
       </c>
       <c r="D5" s="5">
-        <f>D7*I10^2</f>
-        <v>2.9502330000000003</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="8" t="s">
+        <f>D7*H10^2</f>
+        <v>5.9004660000000007</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="9">
-        <f>H2^0.2</f>
-        <v>1.9241536043888867</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="K5" s="13">
-        <f>K2*(C6-C7)/(D6-D7)</f>
-        <v>1.0033444816053512</v>
-      </c>
-      <c r="L5" s="3"/>
-    </row>
-    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="9">
+        <f>G2^0.2</f>
+        <v>2.2102720801231301</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="13">
+        <f>J2*(C6-C7)/(D6-D7)</f>
+        <v>1.3377926421404682</v>
+      </c>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="11">
         <f t="shared" si="0"/>
-        <v>0.33</v>
+        <v>0.66</v>
       </c>
       <c r="D6" s="5">
-        <f>D7*I10</f>
-        <v>0.98670000000000013</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="14">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="5" t="s">
+        <f>D7*H10</f>
+        <v>1.9734000000000003</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="G6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="16">
-        <f>K3*(C6-C7)/(D5-D6)</f>
-        <v>1.0067001487679108</v>
-      </c>
-      <c r="L6" s="3"/>
-    </row>
-    <row r="7" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="I6" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="16">
+        <f>J3*(C6-C7)/(D5-D6)</f>
+        <v>1.7896891533651751</v>
+      </c>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="3"/>
       <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="11">
         <f t="shared" si="0"/>
-        <v>0.11036789297658862</v>
+        <v>0.22073578595317725</v>
       </c>
       <c r="D7" s="17">
-        <v>0.33</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="5" t="s">
+        <v>0.66</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="19">
-        <f>ABS(K5-1)+ABS(K6-1)</f>
-        <v>1.0044630373261976E-2</v>
-      </c>
-      <c r="L7" s="3"/>
-    </row>
-    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="19">
+        <f>ABS(J5-1)+ABS(J6-1)</f>
+        <v>1.1274817955056433</v>
+      </c>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="3"/>
       <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="11">
         <f t="shared" si="0"/>
-        <v>3.691233878815673E-2</v>
+        <v>7.3824677576313461E-2</v>
       </c>
       <c r="D8" s="5">
-        <f>D7/I10</f>
-        <v>0.11036789297658862</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G8" s="5">
-        <f>K2-0.5</f>
-        <v>2.5</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="9">
-        <f>K2+0.5</f>
+        <f>D7/H10</f>
+        <v>0.22073578595317725</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="5">
+        <f>J2-0.5</f>
         <v>3.5</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="G8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="9">
+        <f>J2+0.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="I8" s="5"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="3"/>
       <c r="B9" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="21">
         <f t="shared" si="0"/>
-        <v>1.2345263808748069E-2</v>
+        <v>2.4690527617496138E-2</v>
       </c>
       <c r="D9" s="5">
-        <f>D7/I10^2</f>
-        <v>3.691233878815673E-2</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7" t="s">
+        <f>D7/H10^2</f>
+        <v>7.3824677576313461E-2</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="5">
+        <f>J4-0.5</f>
+        <v>3.5</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="5">
-        <f>K4-0.5</f>
-        <v>2.5</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="9">
-        <f>K4+0.5</f>
-        <v>3.5</v>
-      </c>
-      <c r="J9" s="5"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H9" s="9">
+        <f>J4+0.5</f>
+        <v>4.5</v>
+      </c>
+      <c r="I9" s="5"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="3"/>
       <c r="B10" s="5" t="s">
         <v>1</v>
@@ -1038,25 +1066,24 @@
         <v>0</v>
       </c>
       <c r="D10" s="5">
-        <f>D7/I10^3</f>
-        <v>1.2345263808748069E-2</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="22">
+        <f>D7/H10^3</f>
+        <v>2.4690527617496138E-2</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="22">
         <v>2.99</v>
       </c>
-      <c r="J10" s="5"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="I10" s="5"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="23"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
@@ -1067,10 +1094,9 @@
       <c r="H11" s="23"/>
       <c r="I11" s="23"/>
       <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1079,12 +1105,11 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1093,12 +1118,11 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE1E5BC-DA59-4BF1-B87D-4BA222FB5056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D283E0-7FEA-4859-8B48-D9D5FA4281B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -820,7 +820,7 @@
         <v>9</v>
       </c>
       <c r="J2" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2" s="3"/>
     </row>
@@ -854,7 +854,7 @@
         <v>10</v>
       </c>
       <c r="J3" s="10">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K3" s="3"/>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="J4" s="9">
         <f>SQRT(J3)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" s="3"/>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="J5" s="13">
         <f>J2*(C6-C7)/(D6-D7)</f>
-        <v>1.3377926421404682</v>
+        <v>1.0033444816053512</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="J6" s="16">
         <f>J3*(C6-C7)/(D5-D6)</f>
-        <v>1.7896891533651751</v>
+        <v>1.0067001487679108</v>
       </c>
       <c r="K6" s="3"/>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="J7" s="19">
         <f>ABS(J5-1)+ABS(J6-1)</f>
-        <v>1.1274817955056433</v>
+        <v>1.0044630373261976E-2</v>
       </c>
       <c r="K7" s="3"/>
     </row>
@@ -1013,14 +1013,14 @@
       </c>
       <c r="F8" s="5">
         <f>J2-0.5</f>
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H8" s="9">
         <f>J2+0.5</f>
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="20"/>
@@ -1044,14 +1044,14 @@
       </c>
       <c r="F9" s="5">
         <f>J4-0.5</f>
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>33</v>
       </c>
       <c r="H9" s="9">
         <f>J4+0.5</f>
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="20"/>

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D283E0-7FEA-4859-8B48-D9D5FA4281B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B8EE5C-2868-4BF1-A317-81684961A648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -770,13 +770,13 @@
   <cols>
     <col min="1" max="1" width="4.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="37.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.375" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
@@ -800,7 +800,7 @@
       </c>
       <c r="C2" s="6">
         <f>D3</f>
-        <v>52.750756086600013</v>
+        <v>51.84</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>32</v>
@@ -813,7 +813,7 @@
       </c>
       <c r="G2" s="9">
         <f>C2/1</f>
-        <v>52.750756086600013</v>
+        <v>51.84</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="8" t="s">
@@ -831,11 +831,11 @@
       </c>
       <c r="C3" s="11">
         <f t="shared" ref="C3:C9" si="0">D4</f>
-        <v>17.642393340000005</v>
+        <v>17.28</v>
       </c>
       <c r="D3" s="5">
         <f>D7*H10^4</f>
-        <v>52.750756086600013</v>
+        <v>51.84</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>22</v>
@@ -845,7 +845,7 @@
       </c>
       <c r="G3" s="9">
         <f>G2^0.25</f>
-        <v>2.6949900879462607</v>
+        <v>2.6832815729997477</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>19</v>
@@ -865,11 +865,11 @@
       </c>
       <c r="C4" s="11">
         <f>D5</f>
-        <v>5.9004660000000007</v>
+        <v>5.76</v>
       </c>
       <c r="D4" s="5">
         <f>D7*H10^3</f>
-        <v>17.642393340000005</v>
+        <v>17.28</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>23</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="G4" s="9">
         <f>G2^(1/3)</f>
-        <v>3.7503882522244463</v>
+        <v>3.7286790071446307</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>20</v>
@@ -900,11 +900,11 @@
       </c>
       <c r="C5" s="11">
         <f>D6</f>
-        <v>1.9734000000000003</v>
+        <v>1.92</v>
       </c>
       <c r="D5" s="5">
         <f>D7*H10^2</f>
-        <v>5.9004660000000007</v>
+        <v>5.76</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>24</v>
@@ -914,7 +914,7 @@
       </c>
       <c r="G5" s="9">
         <f>G2^0.2</f>
-        <v>2.2102720801231301</v>
+        <v>2.2025866295099124</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>21</v>
@@ -924,7 +924,7 @@
       </c>
       <c r="J5" s="13">
         <f>J2*(C6-C7)/(D6-D7)</f>
-        <v>1.0033444816053512</v>
+        <v>1</v>
       </c>
       <c r="K5" s="3"/>
     </row>
@@ -935,11 +935,11 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="0"/>
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="D6" s="5">
         <f>D7*H10</f>
-        <v>1.9734000000000003</v>
+        <v>1.92</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>31</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="J6" s="16">
         <f>J3*(C6-C7)/(D5-D6)</f>
-        <v>1.0067001487679108</v>
+        <v>1</v>
       </c>
       <c r="K6" s="3"/>
     </row>
@@ -969,10 +969,10 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="0"/>
-        <v>0.22073578595317725</v>
+        <v>0.21333333333333335</v>
       </c>
       <c r="D7" s="17">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>25</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="J7" s="19">
         <f>ABS(J5-1)+ABS(J6-1)</f>
-        <v>1.0044630373261976E-2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3"/>
     </row>
@@ -1002,11 +1002,11 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="0"/>
-        <v>7.3824677576313461E-2</v>
+        <v>7.1111111111111111E-2</v>
       </c>
       <c r="D8" s="5">
         <f>D7/H10</f>
-        <v>0.22073578595317725</v>
+        <v>0.21333333333333335</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>26</v>
@@ -1033,11 +1033,11 @@
       </c>
       <c r="C9" s="21">
         <f t="shared" si="0"/>
-        <v>2.4690527617496138E-2</v>
+        <v>2.3703703703703703E-2</v>
       </c>
       <c r="D9" s="5">
         <f>D7/H10^2</f>
-        <v>7.3824677576313461E-2</v>
+        <v>7.1111111111111111E-2</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>27</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D10" s="5">
         <f>D7/H10^3</f>
-        <v>2.4690527617496138E-2</v>
+        <v>2.3703703703703703E-2</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>30</v>
@@ -1077,7 +1077,7 @@
         <v>28</v>
       </c>
       <c r="H10" s="22">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="20"/>

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B8EE5C-2868-4BF1-A317-81684961A648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30B5F24-EA42-4D86-9A9C-F0FE680BC066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="C2" s="6">
         <f>D3</f>
-        <v>51.84</v>
+        <v>72.09</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>32</v>
@@ -813,7 +813,7 @@
       </c>
       <c r="G2" s="9">
         <f>C2/1</f>
-        <v>51.84</v>
+        <v>72.09</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="8" t="s">
@@ -831,11 +831,11 @@
       </c>
       <c r="C3" s="11">
         <f t="shared" ref="C3:C9" si="0">D4</f>
-        <v>17.28</v>
+        <v>24.03</v>
       </c>
       <c r="D3" s="5">
         <f>D7*H10^4</f>
-        <v>51.84</v>
+        <v>72.09</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>22</v>
@@ -845,7 +845,7 @@
       </c>
       <c r="G3" s="9">
         <f>G2^0.25</f>
-        <v>2.6832815729997477</v>
+        <v>2.9138605009250087</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>19</v>
@@ -865,11 +865,11 @@
       </c>
       <c r="C4" s="11">
         <f>D5</f>
-        <v>5.76</v>
+        <v>8.01</v>
       </c>
       <c r="D4" s="5">
         <f>D7*H10^3</f>
-        <v>17.28</v>
+        <v>24.03</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>23</v>
@@ -879,7 +879,7 @@
       </c>
       <c r="G4" s="9">
         <f>G2^(1/3)</f>
-        <v>3.7286790071446307</v>
+        <v>4.1619003275395023</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>20</v>
@@ -900,11 +900,11 @@
       </c>
       <c r="C5" s="11">
         <f>D6</f>
-        <v>1.92</v>
+        <v>2.67</v>
       </c>
       <c r="D5" s="5">
         <f>D7*H10^2</f>
-        <v>5.76</v>
+        <v>8.01</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>24</v>
@@ -914,7 +914,7 @@
       </c>
       <c r="G5" s="9">
         <f>G2^0.2</f>
-        <v>2.2025866295099124</v>
+        <v>2.3527457907611757</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>21</v>
@@ -935,11 +935,11 @@
       </c>
       <c r="C6" s="11">
         <f t="shared" si="0"/>
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="D6" s="5">
         <f>D7*H10</f>
-        <v>1.92</v>
+        <v>2.67</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>31</v>
@@ -969,10 +969,10 @@
       </c>
       <c r="C7" s="11">
         <f t="shared" si="0"/>
-        <v>0.21333333333333335</v>
+        <v>0.29666666666666669</v>
       </c>
       <c r="D7" s="17">
-        <v>0.64</v>
+        <v>0.89</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>25</v>
@@ -1002,11 +1002,11 @@
       </c>
       <c r="C8" s="11">
         <f t="shared" si="0"/>
-        <v>7.1111111111111111E-2</v>
+        <v>9.8888888888888887E-2</v>
       </c>
       <c r="D8" s="5">
         <f>D7/H10</f>
-        <v>0.21333333333333335</v>
+        <v>0.29666666666666669</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>26</v>
@@ -1033,11 +1033,11 @@
       </c>
       <c r="C9" s="21">
         <f t="shared" si="0"/>
-        <v>2.3703703703703703E-2</v>
+        <v>3.2962962962962965E-2</v>
       </c>
       <c r="D9" s="5">
         <f>D7/H10^2</f>
-        <v>7.1111111111111111E-2</v>
+        <v>9.8888888888888887E-2</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>27</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D10" s="5">
         <f>D7/H10^3</f>
-        <v>2.3703703703703703E-2</v>
+        <v>3.2962962962962965E-2</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>30</v>

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A30B5F24-EA42-4D86-9A9C-F0FE680BC066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A124CD47-9222-4572-AC18-379A175EB8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -305,7 +305,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0D1117"/>
+        <fgColor rgb="FF242534"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,14 +423,11 @@
   </cellStyleXfs>
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="177" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -477,6 +474,9 @@
     </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,6 +486,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF242534"/>
+      <color rgb="FF202038"/>
+      <color rgb="FF121520"/>
       <color rgb="FF0DB374"/>
       <color rgb="FF0D1117"/>
     </mruColors>
@@ -768,359 +771,359 @@
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.125" style="1"/>
+    <col min="1" max="1" width="4.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="19.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="3"/>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <f>D3</f>
-        <v>72.09</v>
-      </c>
-      <c r="D2" s="7" t="s">
+        <v>80.19</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="8">
         <f>C2/1</f>
-        <v>72.09</v>
-      </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="8" t="s">
+        <v>80.19</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="9">
         <v>3</v>
       </c>
-      <c r="K2" s="3"/>
+      <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="3"/>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <f t="shared" ref="C3:C9" si="0">D4</f>
-        <v>24.03</v>
-      </c>
-      <c r="D3" s="5">
+        <v>26.73</v>
+      </c>
+      <c r="D3" s="4">
         <f>D7*H10^4</f>
-        <v>72.09</v>
-      </c>
-      <c r="E3" s="7" t="s">
+        <v>80.19</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="8">
         <f>G2^0.25</f>
-        <v>2.9138605009250087</v>
-      </c>
-      <c r="H3" s="5" t="s">
+        <v>2.9924717098010434</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="9">
         <v>9</v>
       </c>
-      <c r="K3" s="3"/>
+      <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A4" s="3"/>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="1"/>
+      <c r="B4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <f>D5</f>
-        <v>8.01</v>
-      </c>
-      <c r="D4" s="5">
+        <v>8.91</v>
+      </c>
+      <c r="D4" s="4">
         <f>D7*H10^3</f>
-        <v>24.03</v>
-      </c>
-      <c r="E4" s="7" t="s">
+        <v>26.73</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="8">
         <f>G2^(1/3)</f>
-        <v>4.1619003275395023</v>
-      </c>
-      <c r="H4" s="5" t="s">
+        <v>4.3122778713565051</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="8">
         <f>SQRT(J3)</f>
         <v>3</v>
       </c>
-      <c r="K4" s="3"/>
+      <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="3"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <f>D6</f>
-        <v>2.67</v>
-      </c>
-      <c r="D5" s="5">
+        <v>2.9699999999999998</v>
+      </c>
+      <c r="D5" s="4">
         <f>D7*H10^2</f>
-        <v>8.01</v>
-      </c>
-      <c r="E5" s="7" t="s">
+        <v>8.91</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="8">
         <f>G2^0.2</f>
-        <v>2.3527457907611757</v>
-      </c>
-      <c r="H5" s="5" t="s">
+        <v>2.4033888537025008</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <f>J2*(C6-C7)/(D6-D7)</f>
         <v>1</v>
       </c>
-      <c r="K5" s="3"/>
+      <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="3"/>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="1"/>
+      <c r="B6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <f t="shared" si="0"/>
-        <v>0.89</v>
-      </c>
-      <c r="D6" s="5">
+        <v>0.99</v>
+      </c>
+      <c r="D6" s="4">
         <f>D7*H10</f>
-        <v>2.67</v>
-      </c>
-      <c r="E6" s="14" t="s">
+        <v>2.9699999999999998</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="15">
         <f>J3*(C6-C7)/(D5-D6)</f>
-        <v>1</v>
-      </c>
-      <c r="K6" s="3"/>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="3"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <f t="shared" si="0"/>
-        <v>0.29666666666666669</v>
-      </c>
-      <c r="D7" s="17">
-        <v>0.89</v>
-      </c>
-      <c r="E7" s="7" t="s">
+        <v>0.33</v>
+      </c>
+      <c r="D7" s="16">
+        <v>0.99</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="18">
         <f>ABS(J5-1)+ABS(J6-1)</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="3"/>
+        <v>1.1102230246251565E-16</v>
+      </c>
+      <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="3"/>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <f t="shared" si="0"/>
-        <v>9.8888888888888887E-2</v>
-      </c>
-      <c r="D8" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="D8" s="4">
         <f>D7/H10</f>
-        <v>0.29666666666666669</v>
-      </c>
-      <c r="E8" s="7" t="s">
+        <v>0.33</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <f>J2-0.5</f>
         <v>2.5</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <f>J2+0.5</f>
         <v>3.5</v>
       </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="3"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="3"/>
-      <c r="B9" s="5" t="s">
+      <c r="A9" s="1"/>
+      <c r="B9" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="20">
         <f t="shared" si="0"/>
-        <v>3.2962962962962965E-2</v>
-      </c>
-      <c r="D9" s="5">
+        <v>3.6666666666666667E-2</v>
+      </c>
+      <c r="D9" s="4">
         <f>D7/H10^2</f>
-        <v>9.8888888888888887E-2</v>
-      </c>
-      <c r="E9" s="7" t="s">
+        <v>0.11</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <f>J4-0.5</f>
         <v>2.5</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <f>J4+0.5</f>
         <v>3.5</v>
       </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="3"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="3"/>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="1"/>
+      <c r="B10" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>0</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <f>D7/H10^3</f>
-        <v>3.2962962962962965E-2</v>
-      </c>
-      <c r="E10" s="7" t="s">
+        <v>3.6666666666666667E-2</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="8" t="s">
+      <c r="F10" s="4"/>
+      <c r="G10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="21">
         <v>3</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="3"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="3"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A124CD47-9222-4572-AC18-379A175EB8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45C8C51-D269-4D8A-8580-03A610C5456B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45C8C51-D269-4D8A-8580-03A610C5456B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C3BC5E-6B40-42EE-BD72-18D72810BAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -773,7 +773,8 @@
   <cols>
     <col min="1" max="1" width="4.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.375" style="3" customWidth="1"/>
     <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.625" style="3" bestFit="1" customWidth="1"/>

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07C3BC5E-6B40-42EE-BD72-18D72810BAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8B92FB-4E4B-4235-91D9-2E31E94AA786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8B92FB-4E4B-4235-91D9-2E31E94AA786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5A22E1-9C4A-47FD-B2C9-B9CA38ABD7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5A22E1-9C4A-47FD-B2C9-B9CA38ABD7D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C7396C-E427-441B-9DF3-DD6E16C627B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C7396C-E427-441B-9DF3-DD6E16C627B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B311C1-D1D1-4593-A30C-3E7C483327D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -938,7 +938,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="10">
-        <f t="shared" si="0"/>
+        <f>D7</f>
         <v>0.99</v>
       </c>
       <c r="D6" s="4">

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B311C1-D1D1-4593-A30C-3E7C483327D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AD1380-33A7-4A79-A767-C9E162856936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -777,7 +777,7 @@
     <col min="4" max="4" width="15.375" style="3" customWidth="1"/>
     <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="3" customWidth="1"/>
     <col min="8" max="8" width="37.375" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.875" style="23" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" style="3" bestFit="1" customWidth="1"/>

--- a/Tiering Calculation.xlsx
+++ b/Tiering Calculation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\DAHAKA-s-Filter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AD1380-33A7-4A79-A767-C9E162856936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D090155-5F20-4E6C-8730-5F8624AE5040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -773,11 +773,10 @@
   <cols>
     <col min="1" max="1" width="4.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="19.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.375" style="3" customWidth="1"/>
+    <col min="3" max="4" width="14.75" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.875" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="38" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="37.375" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.875" style="23" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" style="3" bestFit="1" customWidth="1"/>
@@ -804,7 +803,7 @@
       </c>
       <c r="C2" s="5">
         <f>D3</f>
-        <v>80.19</v>
+        <v>240.57000000000002</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>32</v>
@@ -817,7 +816,7 @@
       </c>
       <c r="G2" s="8">
         <f>C2/1</f>
-        <v>80.19</v>
+        <v>240.57000000000002</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="7" t="s">
@@ -835,11 +834,11 @@
       </c>
       <c r="C3" s="10">
         <f t="shared" ref="C3:C9" si="0">D4</f>
-        <v>26.73</v>
+        <v>80.190000000000012</v>
       </c>
       <c r="D3" s="4">
         <f>D7*H10^4</f>
-        <v>80.19</v>
+        <v>240.57000000000002</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>22</v>
@@ -849,7 +848,7 @@
       </c>
       <c r="G3" s="8">
         <f>G2^0.25</f>
-        <v>2.9924717098010434</v>
+        <v>3.9383142517646657</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>19</v>
@@ -869,11 +868,11 @@
       </c>
       <c r="C4" s="10">
         <f>D5</f>
-        <v>8.91</v>
+        <v>26.73</v>
       </c>
       <c r="D4" s="4">
         <f>D7*H10^3</f>
-        <v>26.73</v>
+        <v>80.190000000000012</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>23</v>
@@ -883,7 +882,7 @@
       </c>
       <c r="G4" s="8">
         <f>G2^(1/3)</f>
-        <v>4.3122778713565051</v>
+        <v>6.2193809070100663</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>20</v>
@@ -904,11 +903,11 @@
       </c>
       <c r="C5" s="10">
         <f>D6</f>
-        <v>2.9699999999999998</v>
+        <v>8.91</v>
       </c>
       <c r="D5" s="4">
         <f>D7*H10^2</f>
-        <v>8.91</v>
+        <v>26.73</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>24</v>
@@ -918,7 +917,7 @@
       </c>
       <c r="G5" s="8">
         <f>G2^0.2</f>
-        <v>2.4033888537025008</v>
+        <v>2.9939758549842774</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>21</v>
@@ -939,11 +938,11 @@
       </c>
       <c r="C6" s="10">
         <f>D7</f>
-        <v>0.99</v>
+        <v>2.97</v>
       </c>
       <c r="D6" s="4">
         <f>D7*H10</f>
-        <v>2.9699999999999998</v>
+        <v>8.91</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>31</v>
@@ -962,7 +961,7 @@
       </c>
       <c r="J6" s="15">
         <f>J3*(C6-C7)/(D5-D6)</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="K6" s="1"/>
     </row>
@@ -973,10 +972,10 @@
       </c>
       <c r="C7" s="10">
         <f t="shared" si="0"/>
-        <v>0.33</v>
+        <v>0.9900000000000001</v>
       </c>
       <c r="D7" s="16">
-        <v>0.99</v>
+        <v>2.97</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>25</v>
@@ -995,7 +994,7 @@
       </c>
       <c r="J7" s="18">
         <f>ABS(J5-1)+ABS(J6-1)</f>
-        <v>1.1102230246251565E-16</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1"/>
     </row>
@@ -1006,11 +1005,11 @@
       </c>
       <c r="C8" s="10">
         <f t="shared" si="0"/>
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="D8" s="4">
         <f>D7/H10</f>
-        <v>0.33</v>
+        <v>0.9900000000000001</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>26</v>
@@ -1037,11 +1036,11 @@
       </c>
       <c r="C9" s="20">
         <f t="shared" si="0"/>
-        <v>3.6666666666666667E-2</v>
+        <v>0.11</v>
       </c>
       <c r="D9" s="4">
         <f>D7/H10^2</f>
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>27</v>
@@ -1071,7 +1070,7 @@
       </c>
       <c r="D10" s="4">
         <f>D7/H10^3</f>
-        <v>3.6666666666666667E-2</v>
+        <v>0.11</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>30</v>
